--- a/Entrega 02/Arratia_Cobertura_mediatica_database/06_Recuento_noticias.xlsx
+++ b/Entrega 02/Arratia_Cobertura_mediatica_database/06_Recuento_noticias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/carolina_olave_uc_cl/Documents/7mo semestre/Narración gráfica de no ficción/Proyecto-Arratia-Bravo-Finkenberger/Entrega 02/Arratia_Cobertura_mediatica_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{D45772D2-D807-432A-A34D-B126899D46C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8037685-1027-4603-A913-32044D7B9FD8}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{D45772D2-D807-432A-A34D-B126899D46C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA581AD-FE8D-4CB6-939C-D4AF469FB84E}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{FBBD2732-76A7-4ECD-89F4-3B19F183B60C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{FBBD2732-76A7-4ECD-89F4-3B19F183B60C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,34 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
-  <si>
-    <t>17 - caracol de Paposo</t>
-  </si>
-  <si>
-    <t>214 - huemul</t>
-  </si>
-  <si>
-    <t>215 - ranita de Darwin</t>
-  </si>
-  <si>
-    <t>216 - pingüino de Humboldt</t>
-  </si>
-  <si>
-    <t>25 - picaflor de Arica</t>
-  </si>
-  <si>
-    <t>45 - lagarto gruñidor de Álvaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49 - ranita </t>
-  </si>
-  <si>
-    <t>50 - borrachito</t>
-  </si>
-  <si>
-    <t>51 - picaflor de Juan Fernández</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>Etiqueta</t>
   </si>
@@ -113,73 +86,133 @@
     <t>Chilina angusta</t>
   </si>
   <si>
-    <t>caracol de Paposo</t>
-  </si>
-  <si>
     <t>Gasotropoda</t>
   </si>
   <si>
     <t>Hippocamelus bisulcus</t>
   </si>
   <si>
-    <t>huemul, taruca, wümul, güemul, shoan, shoen, trula, hueque, ciervo sur andino</t>
-  </si>
-  <si>
     <t>Mammalia</t>
   </si>
   <si>
     <t>Rhinoderma darwinii</t>
   </si>
   <si>
-    <t>ranita de Darwin</t>
-  </si>
-  <si>
     <t>Amphibia</t>
   </si>
   <si>
     <t>Spheniscus humboldti</t>
   </si>
   <si>
-    <t>pingüino de Humboldt, pingüino, pájaro niño, patranka, Humboldt Penguin (inglés), Peruvian penguin (inglés)</t>
-  </si>
-  <si>
     <t>Aves</t>
   </si>
   <si>
     <t>Eulidia yarrellii</t>
   </si>
   <si>
-    <t>picaflor de Arica, estrellita chilena</t>
-  </si>
-  <si>
     <t>Pristidactylus alvaroi</t>
   </si>
   <si>
-    <t>lagarto gruñidor de Álvaro</t>
-  </si>
-  <si>
     <t>Reptilia</t>
   </si>
   <si>
     <t>Rhinoderma rufum</t>
   </si>
   <si>
-    <t xml:space="preserve">ranita </t>
-  </si>
-  <si>
     <t>Sclerostomulus nitidus</t>
   </si>
   <si>
-    <t>borrachito</t>
-  </si>
-  <si>
     <t>Insecta</t>
   </si>
   <si>
     <t>Sephanoides fernandensis</t>
   </si>
   <si>
-    <t>picaflor de Juan Fernández</t>
+    <t>Link foto</t>
+  </si>
+  <si>
+    <t>Ficha técnia</t>
+  </si>
+  <si>
+    <t>Caracol de Paposo</t>
+  </si>
+  <si>
+    <t>Huemul</t>
+  </si>
+  <si>
+    <t>Ranita de Darwin</t>
+  </si>
+  <si>
+    <t>Pingüino de Humboldt</t>
+  </si>
+  <si>
+    <t>Picaflor de Arica</t>
+  </si>
+  <si>
+    <t>Lagarto gruñidor de Álvaro</t>
+  </si>
+  <si>
+    <t>Ranita de Darwin del Norte</t>
+  </si>
+  <si>
+    <t>Borrachito</t>
+  </si>
+  <si>
+    <t>Picaflor de Juan Fernández</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55263020057_84a2207950.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264061388_d183652526.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55263020062_f44250f42a.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264061568_47bfe31dc6.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264061478_8273248e77.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264324885_5b4d80044b.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264157039_b62cefd96c.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264061428_f0682c5434.jpg</t>
+  </si>
+  <si>
+    <t>https://live.staticflickr.com/65535/55264157119_fa2a0bec27.jpg</t>
+  </si>
+  <si>
+    <t>Vive en costas e islas del norte y centro de Chile. En Peligro (EN), nidifica en cavidades de guano y se ve afectado por la sobrepesca y el cambio climático.</t>
+  </si>
+  <si>
+    <t>Pequeña ave de valles del norte grande. En Peligro (EN), es un insectívoro esencial para su ecosistema, aunque la degradación de los valles desérticos amenaza su equilibrio local.</t>
+  </si>
+  <si>
+    <t>Exclusivo de la Isla Robinson Crusoe. En Peligro Crítico (CR), destaca por su plumaje rojizo único. Es amenazado severamente por gatos, coatíes y la invasión de plantas exóticas en su hábitat.</t>
+  </si>
+  <si>
+    <t>Habita exclusivamente en los oasis de niebla de Antofagasta. Clasificado en Peligro Crítico (CR), este molusco depende de la humedad de las nubes y sufre por la sequía extrema.</t>
+  </si>
+  <si>
+    <t>Reside en los bosques andino-patagónicos. En estado En Peligro (EN), este ciervo emblemático es Monumento Natural y enfrenta amenazas como ataques de perros, enfermedades ganaderas y fragmentación de hábitat.</t>
+  </si>
+  <si>
+    <t>Habita bosques templados del sur. En estado En Peligro (EN), destaca porque el macho incuba los renacuajos en su saco vocal. Sus poblaciones declinan por el hongo quítrido y la deforestación.</t>
+  </si>
+  <si>
+    <t>Habita valles de la Región de Arica. En Peligro Crítico (CR), es el ave más pequeña del país. Su extinción es inminente debido al uso de pesticidas y pérdida de vegetación.</t>
+  </si>
+  <si>
+    <t>Endémico de la Cordillera de la Costa central. En Peligro Crítico (CR), emite sonidos al ser amenazado. Su hábitat en cumbres boscosas como el Cerro El Roble es vulnerable a incendios.</t>
+  </si>
+  <si>
+    <t>Habitaba la zona central (Maule a Biobío). En Peligro Crítico (CR) y probablemente extinta, su desaparición se vincula a la pérdida de bosque nativo y la propagación de enfermedades fúngicas.</t>
   </si>
 </sst>
 </file>
@@ -246,19 +279,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -269,7 +317,14 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -295,16 +350,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -319,21 +364,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B9679F1-BFBC-4FAF-941C-9807037A2060}" name="Tabla1" displayName="Tabla1" ref="A1:J10" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="6">
-  <autoFilter ref="A1:J10" xr:uid="{4B9679F1-BFBC-4FAF-941C-9807037A2060}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4B9679F1-BFBC-4FAF-941C-9807037A2060}" name="Tabla1" displayName="Tabla1" ref="A1:L10" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6">
+  <autoFilter ref="A1:L10" xr:uid="{4B9679F1-BFBC-4FAF-941C-9807037A2060}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{734952E6-08A5-47CB-856F-684411156B4C}" name="Etiqueta" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{496254C8-B58D-495A-9AF0-29BB873A8D02}" name="Nombre científico" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{279F9FED-0AEA-4001-9E0B-D325EBA8E50F}" name="Nombre común" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{731343DF-32A0-4912-BF9C-FC30C57B033B}" name="Clase" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{496254C8-B58D-495A-9AF0-29BB873A8D02}" name="Nombre científico" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{279F9FED-0AEA-4001-9E0B-D325EBA8E50F}" name="Nombre común" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{731343DF-32A0-4912-BF9C-FC30C57B033B}" name="Clase" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{C0BBBD89-A13C-470C-ACC2-87319C8322BD}" name="RCE"/>
     <tableColumn id="11" xr3:uid="{11219332-245F-4133-8CF5-95C8E5AB329C}" name="Endémica"/>
     <tableColumn id="2" xr3:uid="{88AF2E90-3CC6-4CEF-B431-DCA227E403FF}" name="Apariciones"/>
     <tableColumn id="3" xr3:uid="{13500D59-0FF2-4093-AD93-BF9132B8D0C4}" name="Protagonista"/>
-    <tableColumn id="6" xr3:uid="{42DA7CE7-7F5F-4B19-930F-BB7CFC4D6882}" name="% Protagonismo" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{42DA7CE7-7F5F-4B19-930F-BB7CFC4D6882}" name="% Protagonismo" dataDxfId="1">
       <calculatedColumnFormula>SUM(H2/G2)*100</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{E5F9844F-0F95-455D-A793-B99843115FA3}" name="Foto"/>
+    <tableColumn id="4" xr3:uid="{AE210E72-DF21-40F8-B82A-FED84C256D10}" name="Link foto"/>
+    <tableColumn id="5" xr3:uid="{9D1F7149-5606-4D59-AB8B-66B79D411DBA}" name="Ficha técnia" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -656,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2039666E-7B3C-472C-894D-3C9D90AD1428}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.6328125" bestFit="1" customWidth="1"/>
@@ -666,58 +713,65 @@
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.1796875" customWidth="1"/>
+    <col min="12" max="12" width="32.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -732,25 +786,31 @@
       <c r="J2">
         <v>3</v>
       </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
+    <row r="3" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>214</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -765,25 +825,31 @@
       <c r="J3">
         <v>8</v>
       </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>29</v>
+    <row r="4" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>215</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>24</v>
@@ -798,25 +864,31 @@
       <c r="J4">
         <v>24</v>
       </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>32</v>
+    <row r="5" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>216</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>76</v>
@@ -831,25 +903,31 @@
       <c r="J5">
         <v>76</v>
       </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -864,25 +942,31 @@
       <c r="J6">
         <v>8</v>
       </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>37</v>
+    <row r="7" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>9</v>
@@ -897,25 +981,31 @@
       <c r="J7">
         <v>8</v>
       </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>40</v>
+    <row r="8" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G8">
         <v>13</v>
@@ -930,25 +1020,31 @@
       <c r="J8">
         <v>13</v>
       </c>
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" t="s">
         <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -963,25 +1059,31 @@
       <c r="J9">
         <v>1</v>
       </c>
+      <c r="K9" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>45</v>
+    <row r="10" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>51</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -995,6 +1097,12 @@
       </c>
       <c r="J10">
         <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Entrega 02/Arratia_Cobertura_mediatica_database/06_Recuento_noticias.xlsx
+++ b/Entrega 02/Arratia_Cobertura_mediatica_database/06_Recuento_noticias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uccl0-my.sharepoint.com/personal/carolina_olave_uc_cl/Documents/7mo semestre/Narración gráfica de no ficción/Proyecto-Arratia-Bravo-Finkenberger/Entrega 02/Arratia_Cobertura_mediatica_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{D45772D2-D807-432A-A34D-B126899D46C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA581AD-FE8D-4CB6-939C-D4AF469FB84E}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{D45772D2-D807-432A-A34D-B126899D46C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFDB3EFC-E751-4EC4-AACE-BE8FD40E0FCA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{FBBD2732-76A7-4ECD-89F4-3B19F183B60C}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Chilina angusta</t>
   </si>
   <si>
-    <t>Gasotropoda</t>
-  </si>
-  <si>
     <t>Hippocamelus bisulcus</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>Link foto</t>
   </si>
   <si>
-    <t>Ficha técnia</t>
-  </si>
-  <si>
     <t>Caracol de Paposo</t>
   </si>
   <si>
@@ -213,6 +207,12 @@
   </si>
   <si>
     <t>Habitaba la zona central (Maule a Biobío). En Peligro Crítico (CR) y probablemente extinta, su desaparición se vincula a la pérdida de bosque nativo y la propagación de enfermedades fúngicas.</t>
+  </si>
+  <si>
+    <t>Ficha técnica</t>
+  </si>
+  <si>
+    <t>Gastropoda</t>
   </si>
 </sst>
 </file>
@@ -279,18 +279,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -380,7 +379,7 @@
     </tableColumn>
     <tableColumn id="7" xr3:uid="{E5F9844F-0F95-455D-A793-B99843115FA3}" name="Foto"/>
     <tableColumn id="4" xr3:uid="{AE210E72-DF21-40F8-B82A-FED84C256D10}" name="Link foto"/>
-    <tableColumn id="5" xr3:uid="{9D1F7149-5606-4D59-AB8B-66B79D411DBA}" name="Ficha técnia" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{9D1F7149-5606-4D59-AB8B-66B79D411DBA}" name="Ficha técnica" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -747,25 +746,25 @@
       <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>30</v>
+      <c r="K1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>17</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -787,10 +786,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="101.5" x14ac:dyDescent="0.35">
@@ -798,13 +797,13 @@
         <v>214</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -826,10 +825,10 @@
         <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
@@ -837,13 +836,13 @@
         <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -865,10 +864,10 @@
         <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>54</v>
+        <v>39</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
@@ -876,13 +875,13 @@
         <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -904,10 +903,10 @@
         <v>76</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
@@ -915,13 +914,13 @@
         <v>25</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
@@ -943,10 +942,10 @@
         <v>8</v>
       </c>
       <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>55</v>
+        <v>42</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
@@ -954,13 +953,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
         <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
@@ -982,10 +981,10 @@
         <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>56</v>
+        <v>43</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="87" x14ac:dyDescent="0.35">
@@ -993,13 +992,13 @@
         <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
@@ -1021,10 +1020,10 @@
         <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
@@ -1032,13 +1031,13 @@
         <v>50</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
       </c>
       <c r="E9" t="s">
         <v>3</v>
@@ -1060,10 +1059,10 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="87" x14ac:dyDescent="0.35">
@@ -1071,13 +1070,13 @@
         <v>51</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
         <v>3</v>
@@ -1099,10 +1098,10 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
